--- a/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_40c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B7993E9-B46E-4877-AD83-1935951A545F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AE3CD9F-3F12-4177-BCB3-3CFFFE6B45E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -681,13 +681,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S01aH03,S01aH02,S04aH04,S04aH02,S01aH04,S01aH07,S02aH07,S03aH04,S02aH02,S04aH06,S04aH05,S04aH08,S01aH06,S02aH03,S03aH03,S04aH03,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</t>
+    <t>S02aH04,S02aH05,S02aH02,S04aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S01aH03,S03aH02,S03aH04,S04aH06,S01aH06,S02aH03,S01aH02,S04aH04,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH09,S03aH08,S03aH10,S01aH08,S02aH08,S01aH10,S03aH02,S01aH09,S02aH09,S04aH09,S03aH01,S01aH01,S04aH01,S02aH02,S04aH10,S02aH01,S02aH10,S04aH02,S01aH02,S04aH08</t>
+    <t>S03aH08,S03aH10,S03aH01,S01aH10,S03aH02,S01aH09,S04aH02,S04aH08,S02aH09,S04aH09,S01aH01,S04aH01,S01aH08,S02aH08,S02aH01,S02aH10,S03aH09,S02aH02,S04aH10,S01aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH09,S03aH08,S03aH10,S01aH08,S02aH08,S01aH10,S03aH02,S01aH09,S02aH09,S04aH09,S03aH01,S01aH01,S04aH01,S02aH02,S04aH10,S02aH01,S02aH10,S04aH02,S01aH02,S04aH08</v>
+        <v>S03aH08,S03aH10,S03aH01,S01aH10,S03aH02,S01aH09,S04aH02,S04aH08,S02aH09,S04aH09,S01aH01,S04aH01,S01aH08,S02aH08,S02aH01,S02aH10,S03aH09,S02aH02,S04aH10,S01aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH06,S03aH05,S03aH08,S04aH07,S02aH04,S02aH05,S01aH03,S01aH02,S04aH04,S04aH02,S01aH04,S01aH07,S02aH07,S03aH04,S02aH02,S04aH06,S04aH05,S04aH08,S01aH06,S02aH03,S03aH03,S04aH03,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</v>
+        <v>S02aH04,S02aH05,S02aH02,S04aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S01aH03,S03aH02,S03aH04,S04aH06,S01aH06,S02aH03,S01aH02,S04aH04,S04aH03,S02aH06,S03aH05,S03aH08,S04aH07,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1410,7 +1410,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDCA4B4C-005F-4C89-86D1-57D550E61468}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD60A710-F8DE-4488-99AB-AD0D06449782}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1548,7 +1548,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6144C49-C12F-4D98-929D-5540C68D7E19}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F8E5F69-1728-4413-B3F4-F2EA3916FEEC}">
   <dimension ref="B9:O810"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -27210,7 +27210,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6FA8AFF-A204-4406-A2BB-D67E2D6DCBAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ADB6A75-B4F2-4C9B-927A-2C1C6410CABF}">
   <dimension ref="B9:FT60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -41663,7 +41663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73794C23-7258-40F7-84AF-33A7A4F38672}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F14DBB1E-F462-4E0F-A38C-BB31023C229C}">
   <dimension ref="B9:E50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -42253,7 +42253,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A622EAE-BE14-4629-AD77-4A2FA13FD0FD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24C72F69-1062-4EFD-8B26-CFCB4EABFC7F}">
   <dimension ref="B9:D90"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43160,7 +43160,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{541C07C0-2B91-4C3C-92C5-4458871A35A0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD4563C2-BE62-40F8-BC60-2077A3384CE9}">
   <dimension ref="B9:D50"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43627,7 +43627,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA99F9DE-B979-47F5-9C7B-B18D9543B6F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0281DDDA-90B7-4493-BC02-CB4993C92C96}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -43673,7 +43673,7 @@
         <v>41</v>
       </c>
       <c r="D12">
-        <v>0.17526666666666668</v>
+        <v>0.17526666666666665</v>
       </c>
       <c r="E12" t="s">
         <v>221</v>
@@ -43715,7 +43715,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.20653333333333335</v>
+        <v>0.20653333333333332</v>
       </c>
       <c r="E15" t="s">
         <v>221</v>
@@ -43771,7 +43771,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.23839999999999997</v>
+        <v>0.23840000000000003</v>
       </c>
       <c r="E19" t="s">
         <v>221</v>
@@ -43785,7 +43785,7 @@
         <v>41</v>
       </c>
       <c r="D20">
-        <v>0.23149999999999996</v>
+        <v>0.23150000000000001</v>
       </c>
       <c r="E20" t="s">
         <v>221</v>
@@ -43855,7 +43855,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.24466666666666667</v>
+        <v>0.2446666666666667</v>
       </c>
       <c r="E25" t="s">
         <v>221</v>
@@ -44009,7 +44009,7 @@
         <v>41</v>
       </c>
       <c r="D36">
-        <v>0.32773333333333332</v>
+        <v>0.32773333333333338</v>
       </c>
       <c r="E36" t="s">
         <v>221</v>
@@ -44121,7 +44121,7 @@
         <v>41</v>
       </c>
       <c r="D44">
-        <v>0.34233333333333332</v>
+        <v>0.34233333333333338</v>
       </c>
       <c r="E44" t="s">
         <v>221</v>
@@ -44219,7 +44219,7 @@
         <v>37</v>
       </c>
       <c r="D51">
-        <v>0.3167666666666667</v>
+        <v>0.31676666666666664</v>
       </c>
       <c r="E51" t="s">
         <v>221</v>
@@ -44233,7 +44233,7 @@
         <v>41</v>
       </c>
       <c r="D52">
-        <v>0.3227666666666667</v>
+        <v>0.32276666666666665</v>
       </c>
       <c r="E52" t="s">
         <v>221</v>
@@ -44289,7 +44289,7 @@
         <v>41</v>
       </c>
       <c r="D56">
-        <v>0.34999999999999992</v>
+        <v>0.35000000000000003</v>
       </c>
       <c r="E56" t="s">
         <v>221</v>
@@ -44303,7 +44303,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.18733333333333332</v>
+        <v>0.18733333333333335</v>
       </c>
       <c r="E57" t="s">
         <v>221</v>
@@ -44359,7 +44359,7 @@
         <v>43</v>
       </c>
       <c r="D61">
-        <v>0.20516666666666669</v>
+        <v>0.20516666666666664</v>
       </c>
       <c r="E61" t="s">
         <v>221</v>
@@ -44415,7 +44415,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.20076666666666668</v>
+        <v>0.20076666666666665</v>
       </c>
       <c r="E65" t="s">
         <v>221</v>
@@ -44457,7 +44457,7 @@
         <v>41</v>
       </c>
       <c r="D68">
-        <v>0.38203333333333339</v>
+        <v>0.38203333333333328</v>
       </c>
       <c r="E68" t="s">
         <v>221</v>
@@ -44527,7 +44527,7 @@
         <v>43</v>
       </c>
       <c r="D73">
-        <v>0.19603333333333336</v>
+        <v>0.19603333333333331</v>
       </c>
       <c r="E73" t="s">
         <v>221</v>
@@ -44583,7 +44583,7 @@
         <v>43</v>
       </c>
       <c r="D77">
-        <v>0.21279999999999999</v>
+        <v>0.21280000000000002</v>
       </c>
       <c r="E77" t="s">
         <v>221</v>
@@ -44611,7 +44611,7 @@
         <v>37</v>
       </c>
       <c r="D79">
-        <v>0.32426666666666665</v>
+        <v>0.3242666666666667</v>
       </c>
       <c r="E79" t="s">
         <v>221</v>
@@ -44667,7 +44667,7 @@
         <v>37</v>
       </c>
       <c r="D83">
-        <v>0.30743333333333328</v>
+        <v>0.30743333333333334</v>
       </c>
       <c r="E83" t="s">
         <v>221</v>
@@ -44681,7 +44681,7 @@
         <v>41</v>
       </c>
       <c r="D84">
-        <v>0.33236666666666664</v>
+        <v>0.3323666666666667</v>
       </c>
       <c r="E84" t="s">
         <v>221</v>
@@ -44779,7 +44779,7 @@
         <v>37</v>
       </c>
       <c r="D91">
-        <v>0.31433333333333335</v>
+        <v>0.3143333333333333</v>
       </c>
       <c r="E91" t="s">
         <v>221</v>
@@ -44793,7 +44793,7 @@
         <v>41</v>
       </c>
       <c r="D92">
-        <v>0.31546666666666673</v>
+        <v>0.31546666666666667</v>
       </c>
       <c r="E92" t="s">
         <v>221</v>
@@ -44947,7 +44947,7 @@
         <v>37</v>
       </c>
       <c r="D103">
-        <v>0.28609999999999997</v>
+        <v>0.28610000000000002</v>
       </c>
       <c r="E103" t="s">
         <v>221</v>
@@ -44961,7 +44961,7 @@
         <v>41</v>
       </c>
       <c r="D104">
-        <v>0.32653333333333334</v>
+        <v>0.32653333333333329</v>
       </c>
       <c r="E104" t="s">
         <v>221</v>
@@ -45003,7 +45003,7 @@
         <v>37</v>
       </c>
       <c r="D107">
-        <v>0.32646666666666668</v>
+        <v>0.32646666666666663</v>
       </c>
       <c r="E107" t="s">
         <v>221</v>
@@ -45017,7 +45017,7 @@
         <v>41</v>
       </c>
       <c r="D108">
-        <v>0.32569999999999993</v>
+        <v>0.32569999999999999</v>
       </c>
       <c r="E108" t="s">
         <v>221</v>
@@ -45059,7 +45059,7 @@
         <v>37</v>
       </c>
       <c r="D111">
-        <v>0.31430000000000002</v>
+        <v>0.31429999999999997</v>
       </c>
       <c r="E111" t="s">
         <v>221</v>
@@ -45129,7 +45129,7 @@
         <v>41</v>
       </c>
       <c r="D116">
-        <v>0.32293333333333329</v>
+        <v>0.32293333333333335</v>
       </c>
       <c r="E116" t="s">
         <v>221</v>
@@ -45227,7 +45227,7 @@
         <v>37</v>
       </c>
       <c r="D123">
-        <v>0.30759999999999998</v>
+        <v>0.30760000000000004</v>
       </c>
       <c r="E123" t="s">
         <v>221</v>
@@ -45255,7 +45255,7 @@
         <v>43</v>
       </c>
       <c r="D125">
-        <v>0.17353333333333334</v>
+        <v>0.17353333333333332</v>
       </c>
       <c r="E125" t="s">
         <v>221</v>
